--- a/artfynd/S 722-2026 artfynd.xlsx
+++ b/artfynd/S 722-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135987432</v>
+        <v>135985429</v>
       </c>
       <c r="B2" t="n">
-        <v>5181</v>
+        <v>96488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>2812</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mossbodarna O, Dlr</t>
+          <t>Mossbodarna O., Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515951</v>
+        <v>515969</v>
       </c>
       <c r="R2" t="n">
-        <v>6701992</v>
+        <v>6701943</v>
       </c>
       <c r="S2" t="n">
         <v>6</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,33 +769,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135987432</t>
+          <t>https://artportalen.se/Sighting/135985429</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135987434</v>
+        <v>135985436</v>
       </c>
       <c r="B3" t="n">
-        <v>101485</v>
+        <v>96488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +804,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mossbodarna O, Dlr</t>
+          <t>Mossbodarna O., Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515979</v>
+        <v>515956</v>
       </c>
       <c r="R3" t="n">
-        <v>6701970</v>
+        <v>6701946</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,18 +888,2332 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135985436</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135985422</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>515972</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6701976</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985422</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135985447</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>515944</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6701995</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985447</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135985423</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>515972</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6701976</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985423</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135985425</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>515949</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6701998</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Större flatbagge?????</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985425</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135985426</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>515942</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6702011</v>
+      </c>
+      <c r="S8" t="n">
+        <v>7</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985426</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135987432</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mossbodarna O, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>515951</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6701992</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135987432</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135985446</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>515944</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6701995</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985446</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135985424</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>515969</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6701993</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Två stänglar i fröstadie</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985424</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135985441</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>516012</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6702026</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985441</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135985442</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>516005</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6702038</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>4 stänglar frukt/blommade</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985442</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135985427</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>515964</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6701956</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985427</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135985431</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>515964</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6701942</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985431</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135985432</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>515974</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6701955</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985432</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135985434</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>515962</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6701937</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985434</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135985435</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>515958</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6701948</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985435</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135985437</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>515958</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6701938</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985437</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135987434</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mossbodarna O, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>515979</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6701970</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135987434</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135985433</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98327</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>515983</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6701955</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985433</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135985438</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98327</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>516022</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6701977</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985438</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135985428</v>
+      </c>
+      <c r="B23" t="n">
+        <v>87231</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>515969</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6701955</v>
+      </c>
+      <c r="S23" t="n">
+        <v>6</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985428</t>
         </is>
       </c>
     </row>
@@ -906,6 +3221,26 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 722-2026 artfynd.xlsx
+++ b/artfynd/S 722-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135985429</v>
       </c>
       <c r="B2" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135985436</v>
       </c>
       <c r="B3" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135985422</v>
       </c>
       <c r="B4" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>135985447</v>
       </c>
       <c r="B5" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>135985423</v>
       </c>
       <c r="B6" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>135985425</v>
       </c>
       <c r="B7" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>135985426</v>
       </c>
       <c r="B8" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135987432</v>
       </c>
       <c r="B9" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>135985446</v>
       </c>
       <c r="B10" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>135985424</v>
       </c>
       <c r="B11" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>135985441</v>
       </c>
       <c r="B12" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>135985442</v>
       </c>
       <c r="B13" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>135985427</v>
       </c>
       <c r="B14" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>135985431</v>
       </c>
       <c r="B15" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>135985432</v>
       </c>
       <c r="B16" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>135985434</v>
       </c>
       <c r="B17" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>135985435</v>
       </c>
       <c r="B18" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>135985437</v>
       </c>
       <c r="B19" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>135987434</v>
       </c>
       <c r="B20" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>135985433</v>
       </c>
       <c r="B21" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>135985438</v>
       </c>
       <c r="B22" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>135985428</v>
       </c>
       <c r="B23" t="n">
-        <v>87231</v>
+        <v>87233</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/S 722-2026 artfynd.xlsx
+++ b/artfynd/S 722-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ23"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,50 +905,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135985422</v>
+        <v>136146808</v>
       </c>
       <c r="B4" t="n">
-        <v>4777</v>
+        <v>57867</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>100100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mossbodarna O., Dlr</t>
+          <t>Nyckelbiotop mossbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515972</v>
+        <v>515860</v>
       </c>
       <c r="R4" t="n">
-        <v>6701976</v>
+        <v>6701993</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -975,22 +974,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +998,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,62 +1009,65 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135985422</t>
+          <t>https://artportalen.se/Sighting/136146808</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135985447</v>
+        <v>136146809</v>
       </c>
       <c r="B5" t="n">
-        <v>4777</v>
+        <v>57867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>100100</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mossbodarna O., Dlr</t>
+          <t>Nyckelbiotop mossbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515944</v>
+        <v>515893</v>
       </c>
       <c r="R5" t="n">
-        <v>6701995</v>
+        <v>6702028</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1093,31 +1094,30 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1129,65 +1129,65 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135985447</t>
+          <t>https://artportalen.se/Sighting/136146809</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135985423</v>
+        <v>136146804</v>
       </c>
       <c r="B6" t="n">
-        <v>5182</v>
+        <v>57982</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mossbodarna O., Dlr</t>
+          <t>Nyckelbiotop mossbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515972</v>
+        <v>515929</v>
       </c>
       <c r="R6" t="n">
-        <v>6701976</v>
+        <v>6701908</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,22 +1211,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,62 +1251,62 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135985423</t>
+          <t>https://artportalen.se/Sighting/136146804</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135985425</v>
+        <v>136146806</v>
       </c>
       <c r="B7" t="n">
-        <v>5182</v>
+        <v>57982</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mossbodarna O., Dlr</t>
+          <t>Nyckelbiotop mossbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515949</v>
+        <v>515890</v>
       </c>
       <c r="R7" t="n">
-        <v>6701998</v>
+        <v>6701924</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,27 +1333,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Större flatbagge?????</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,22 +1373,22 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135985425</t>
+          <t>https://artportalen.se/Sighting/136146806</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135985426</v>
+        <v>135985422</v>
       </c>
       <c r="B8" t="n">
-        <v>5182</v>
+        <v>4777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,27 +1396,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1420,13 +1425,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515942</v>
+        <v>515972</v>
       </c>
       <c r="R8" t="n">
-        <v>6702011</v>
+        <v>6701976</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,7 +1470,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,6 +1479,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1491,16 +1497,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135985426</t>
+          <t>https://artportalen.se/Sighting/135985422</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135987432</v>
+        <v>135985447</v>
       </c>
       <c r="B9" t="n">
-        <v>5182</v>
+        <v>4777</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,37 +1514,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mossbodarna O, Dlr</t>
+          <t>Mossbodarna O., Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515951</v>
+        <v>515944</v>
       </c>
       <c r="R9" t="n">
-        <v>6701992</v>
+        <v>6701995</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1567,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,7 +1588,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,33 +1597,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135987432</t>
+          <t>https://artportalen.se/Sighting/135985447</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135985446</v>
+        <v>135985423</v>
       </c>
       <c r="B10" t="n">
-        <v>5202</v>
+        <v>5182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,27 +1632,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1649,10 +1661,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515944</v>
+        <v>515972</v>
       </c>
       <c r="R10" t="n">
-        <v>6701995</v>
+        <v>6701976</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1684,7 +1696,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1694,7 +1706,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,48 +1732,44 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135985446</t>
+          <t>https://artportalen.se/Sighting/135985423</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135985424</v>
+        <v>135985425</v>
       </c>
       <c r="B11" t="n">
-        <v>99293</v>
+        <v>5182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1770,10 +1778,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515969</v>
+        <v>515949</v>
       </c>
       <c r="R11" t="n">
-        <v>6701993</v>
+        <v>6701998</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1805,7 +1813,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1815,12 +1823,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Två stänglar i fröstadie</t>
+          <t>Större flatbagge?????</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,48 +1854,44 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135985424</t>
+          <t>https://artportalen.se/Sighting/135985425</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135985441</v>
+        <v>135985426</v>
       </c>
       <c r="B12" t="n">
-        <v>99293</v>
+        <v>5182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1896,13 +1900,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516012</v>
+        <v>515942</v>
       </c>
       <c r="R12" t="n">
-        <v>6702026</v>
+        <v>6702011</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1931,7 +1935,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1941,7 +1945,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1967,63 +1971,54 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135985441</t>
+          <t>https://artportalen.se/Sighting/135985426</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135985442</v>
+        <v>135987432</v>
       </c>
       <c r="B13" t="n">
-        <v>99293</v>
+        <v>5182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mossbodarna O., Dlr</t>
+          <t>Mossbodarna O, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516005</v>
+        <v>515951</v>
       </c>
       <c r="R13" t="n">
-        <v>6702038</v>
+        <v>6701992</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2052,7 +2047,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2062,12 +2057,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>4 stänglar frukt/blommade</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2082,27 +2072,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135985442</t>
+          <t>https://artportalen.se/Sighting/135987432</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135985427</v>
+        <v>136146803</v>
       </c>
       <c r="B14" t="n">
-        <v>101502</v>
+        <v>5182</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,37 +2100,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mossbodarna O., Dlr</t>
+          <t>Nyckelbiotop mossbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515964</v>
+        <v>515957</v>
       </c>
       <c r="R14" t="n">
-        <v>6701956</v>
+        <v>6701904</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2164,22 +2159,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2199,22 +2194,22 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135985427</t>
+          <t>https://artportalen.se/Sighting/136146803</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135985431</v>
+        <v>136146807</v>
       </c>
       <c r="B15" t="n">
-        <v>101502</v>
+        <v>5182</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,37 +2217,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mossbodarna O., Dlr</t>
+          <t>Nyckelbiotop mossbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515964</v>
+        <v>515872</v>
       </c>
       <c r="R15" t="n">
-        <v>6701942</v>
+        <v>6701954</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2276,22 +2276,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2311,22 +2311,22 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135985431</t>
+          <t>https://artportalen.se/Sighting/136146807</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135985432</v>
+        <v>135985446</v>
       </c>
       <c r="B16" t="n">
-        <v>101502</v>
+        <v>5202</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2334,34 +2334,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mossbodarna O., Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515974</v>
+        <v>515944</v>
       </c>
       <c r="R16" t="n">
-        <v>6701955</v>
+        <v>6701995</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2393,7 +2398,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2403,7 +2408,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2429,51 +2434,60 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135985432</t>
+          <t>https://artportalen.se/Sighting/135985446</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135985434</v>
+        <v>135985424</v>
       </c>
       <c r="B17" t="n">
-        <v>101502</v>
+        <v>99293</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mossbodarna O., Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515962</v>
+        <v>515969</v>
       </c>
       <c r="R17" t="n">
-        <v>6701937</v>
+        <v>6701993</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2505,7 +2519,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2515,7 +2529,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Två stänglar i fröstadie</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2541,51 +2560,60 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135985434</t>
+          <t>https://artportalen.se/Sighting/135985424</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135985435</v>
+        <v>135985441</v>
       </c>
       <c r="B18" t="n">
-        <v>101502</v>
+        <v>99293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mossbodarna O., Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515958</v>
+        <v>516012</v>
       </c>
       <c r="R18" t="n">
-        <v>6701948</v>
+        <v>6702026</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2617,7 +2645,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2627,7 +2655,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2653,54 +2681,63 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135985435</t>
+          <t>https://artportalen.se/Sighting/135985441</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135985437</v>
+        <v>135985442</v>
       </c>
       <c r="B19" t="n">
-        <v>101502</v>
+        <v>99293</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mossbodarna O., Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>515958</v>
+        <v>516005</v>
       </c>
       <c r="R19" t="n">
-        <v>6701938</v>
+        <v>6702038</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2729,7 +2766,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,7 +2776,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>4 stänglar frukt/blommade</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2765,13 +2807,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135985437</t>
+          <t>https://artportalen.se/Sighting/135985442</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135987434</v>
+        <v>135985427</v>
       </c>
       <c r="B20" t="n">
         <v>101502</v>
@@ -2802,14 +2844,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mossbodarna O, Dlr</t>
+          <t>Mossbodarna O., Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515979</v>
+        <v>515964</v>
       </c>
       <c r="R20" t="n">
-        <v>6701970</v>
+        <v>6701956</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2866,27 +2908,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135987434</t>
+          <t>https://artportalen.se/Sighting/135985427</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135985433</v>
+        <v>135985431</v>
       </c>
       <c r="B21" t="n">
-        <v>98344</v>
+        <v>101502</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2894,21 +2936,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>223358</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2918,13 +2960,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515983</v>
+        <v>515964</v>
       </c>
       <c r="R21" t="n">
-        <v>6701955</v>
+        <v>6701942</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2953,7 +2995,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2963,7 +3005,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2989,16 +3031,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135985433</t>
+          <t>https://artportalen.se/Sighting/135985431</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135985438</v>
+        <v>135985432</v>
       </c>
       <c r="B22" t="n">
-        <v>98344</v>
+        <v>101502</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3006,21 +3048,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>223358</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3030,10 +3072,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>516022</v>
+        <v>515974</v>
       </c>
       <c r="R22" t="n">
-        <v>6701977</v>
+        <v>6701955</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3065,7 +3107,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3075,7 +3117,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3101,38 +3143,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135985438</t>
+          <t>https://artportalen.se/Sighting/135985432</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135985428</v>
+        <v>135985434</v>
       </c>
       <c r="B23" t="n">
-        <v>87233</v>
+        <v>101502</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>249278</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3142,13 +3184,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515969</v>
+        <v>515962</v>
       </c>
       <c r="R23" t="n">
-        <v>6701955</v>
+        <v>6701937</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3177,7 +3219,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3187,7 +3229,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3212,6 +3254,678 @@
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985434</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135985435</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>515958</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6701948</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985435</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135985437</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>515958</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6701938</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985437</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135987434</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mossbodarna O, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>515979</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6701970</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135987434</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135985433</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98344</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>515983</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6701955</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985433</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135985438</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98344</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>516022</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6701977</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135985438</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135985428</v>
+      </c>
+      <c r="B29" t="n">
+        <v>87233</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mossbodarna O., Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>515969</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6701955</v>
+      </c>
+      <c r="S29" t="n">
+        <v>6</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135985428</t>
         </is>
@@ -3241,6 +3955,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 722-2026 artfynd.xlsx
+++ b/artfynd/S 722-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135985429</v>
       </c>
       <c r="B2" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135985436</v>
       </c>
       <c r="B3" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>135985424</v>
       </c>
       <c r="B17" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>135985441</v>
       </c>
       <c r="B18" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>135985442</v>
       </c>
       <c r="B19" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135985427</v>
       </c>
       <c r="B20" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135985431</v>
       </c>
       <c r="B21" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>135985432</v>
       </c>
       <c r="B22" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135985434</v>
       </c>
       <c r="B23" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>135985435</v>
       </c>
       <c r="B24" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>135985437</v>
       </c>
       <c r="B25" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>135987434</v>
       </c>
       <c r="B26" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>135985433</v>
       </c>
       <c r="B27" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135985438</v>
       </c>
       <c r="B28" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>135985428</v>
       </c>
       <c r="B29" t="n">
-        <v>87233</v>
+        <v>87234</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/S 722-2026 artfynd.xlsx
+++ b/artfynd/S 722-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135985429</v>
       </c>
       <c r="B2" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135985436</v>
       </c>
       <c r="B3" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>135985424</v>
       </c>
       <c r="B17" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>135985441</v>
       </c>
       <c r="B18" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>135985442</v>
       </c>
       <c r="B19" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135985427</v>
       </c>
       <c r="B20" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135985431</v>
       </c>
       <c r="B21" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>135985432</v>
       </c>
       <c r="B22" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135985434</v>
       </c>
       <c r="B23" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>135985435</v>
       </c>
       <c r="B24" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>135985437</v>
       </c>
       <c r="B25" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>135987434</v>
       </c>
       <c r="B26" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>135985433</v>
       </c>
       <c r="B27" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135985438</v>
       </c>
       <c r="B28" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>135985428</v>
       </c>
       <c r="B29" t="n">
-        <v>87234</v>
+        <v>87235</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/S 722-2026 artfynd.xlsx
+++ b/artfynd/S 722-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135985429</v>
       </c>
       <c r="B2" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135985436</v>
       </c>
       <c r="B3" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136146808</v>
       </c>
       <c r="B4" t="n">
-        <v>57867</v>
+        <v>57868</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136146809</v>
       </c>
       <c r="B5" t="n">
-        <v>57867</v>
+        <v>57868</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>136146804</v>
       </c>
       <c r="B6" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136146806</v>
       </c>
       <c r="B7" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>135985424</v>
       </c>
       <c r="B17" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>135985441</v>
       </c>
       <c r="B18" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>135985442</v>
       </c>
       <c r="B19" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135985427</v>
       </c>
       <c r="B20" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135985431</v>
       </c>
       <c r="B21" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>135985432</v>
       </c>
       <c r="B22" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135985434</v>
       </c>
       <c r="B23" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>135985435</v>
       </c>
       <c r="B24" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>135985437</v>
       </c>
       <c r="B25" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>135987434</v>
       </c>
       <c r="B26" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>135985433</v>
       </c>
       <c r="B27" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135985438</v>
       </c>
       <c r="B28" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>135985428</v>
       </c>
       <c r="B29" t="n">
-        <v>87235</v>
+        <v>87236</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/S 722-2026 artfynd.xlsx
+++ b/artfynd/S 722-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135985429</v>
       </c>
       <c r="B2" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135985436</v>
       </c>
       <c r="B3" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136146808</v>
       </c>
       <c r="B4" t="n">
-        <v>57868</v>
+        <v>57872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136146809</v>
       </c>
       <c r="B5" t="n">
-        <v>57868</v>
+        <v>57872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>136146804</v>
       </c>
       <c r="B6" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136146806</v>
       </c>
       <c r="B7" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>135985424</v>
       </c>
       <c r="B17" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>135985441</v>
       </c>
       <c r="B18" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>135985442</v>
       </c>
       <c r="B19" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135985427</v>
       </c>
       <c r="B20" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135985431</v>
       </c>
       <c r="B21" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>135985432</v>
       </c>
       <c r="B22" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135985434</v>
       </c>
       <c r="B23" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>135985435</v>
       </c>
       <c r="B24" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>135985437</v>
       </c>
       <c r="B25" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>135987434</v>
       </c>
       <c r="B26" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>135985433</v>
       </c>
       <c r="B27" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135985438</v>
       </c>
       <c r="B28" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>135985428</v>
       </c>
       <c r="B29" t="n">
-        <v>87236</v>
+        <v>87242</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/S 722-2026 artfynd.xlsx
+++ b/artfynd/S 722-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135985429</v>
       </c>
       <c r="B2" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135985436</v>
       </c>
       <c r="B3" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136146808</v>
       </c>
       <c r="B4" t="n">
-        <v>57872</v>
+        <v>57873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136146809</v>
       </c>
       <c r="B5" t="n">
-        <v>57872</v>
+        <v>57873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>136146804</v>
       </c>
       <c r="B6" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136146806</v>
       </c>
       <c r="B7" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>135985424</v>
       </c>
       <c r="B17" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>135985441</v>
       </c>
       <c r="B18" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>135985442</v>
       </c>
       <c r="B19" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135985427</v>
       </c>
       <c r="B20" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135985431</v>
       </c>
       <c r="B21" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>135985432</v>
       </c>
       <c r="B22" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135985434</v>
       </c>
       <c r="B23" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>135985435</v>
       </c>
       <c r="B24" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>135985437</v>
       </c>
       <c r="B25" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>135987434</v>
       </c>
       <c r="B26" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>135985433</v>
       </c>
       <c r="B27" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135985438</v>
       </c>
       <c r="B28" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>135985428</v>
       </c>
       <c r="B29" t="n">
-        <v>87242</v>
+        <v>87243</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/S 722-2026 artfynd.xlsx
+++ b/artfynd/S 722-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135985429</v>
       </c>
       <c r="B2" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135985436</v>
       </c>
       <c r="B3" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>135985424</v>
       </c>
       <c r="B17" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>135985441</v>
       </c>
       <c r="B18" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>135985442</v>
       </c>
       <c r="B19" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135985427</v>
       </c>
       <c r="B20" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135985431</v>
       </c>
       <c r="B21" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>135985432</v>
       </c>
       <c r="B22" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135985434</v>
       </c>
       <c r="B23" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>135985435</v>
       </c>
       <c r="B24" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>135985437</v>
       </c>
       <c r="B25" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>135987434</v>
       </c>
       <c r="B26" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>135985433</v>
       </c>
       <c r="B27" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135985438</v>
       </c>
       <c r="B28" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>135985428</v>
       </c>
       <c r="B29" t="n">
-        <v>87243</v>
+        <v>87249</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/S 722-2026 artfynd.xlsx
+++ b/artfynd/S 722-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135985429</v>
       </c>
       <c r="B2" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135985436</v>
       </c>
       <c r="B3" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136146808</v>
       </c>
       <c r="B4" t="n">
-        <v>57873</v>
+        <v>57878</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136146809</v>
       </c>
       <c r="B5" t="n">
-        <v>57873</v>
+        <v>57878</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>136146804</v>
       </c>
       <c r="B6" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136146806</v>
       </c>
       <c r="B7" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>135985424</v>
       </c>
       <c r="B17" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>135985441</v>
       </c>
       <c r="B18" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>135985442</v>
       </c>
       <c r="B19" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135985427</v>
       </c>
       <c r="B20" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135985431</v>
       </c>
       <c r="B21" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>135985432</v>
       </c>
       <c r="B22" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135985434</v>
       </c>
       <c r="B23" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>135985435</v>
       </c>
       <c r="B24" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>135985437</v>
       </c>
       <c r="B25" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>135987434</v>
       </c>
       <c r="B26" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>135985433</v>
       </c>
       <c r="B27" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135985438</v>
       </c>
       <c r="B28" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>135985428</v>
       </c>
       <c r="B29" t="n">
-        <v>87249</v>
+        <v>87256</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/S 722-2026 artfynd.xlsx
+++ b/artfynd/S 722-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135985429</v>
       </c>
       <c r="B2" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135985436</v>
       </c>
       <c r="B3" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>135985424</v>
       </c>
       <c r="B17" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>135985441</v>
       </c>
       <c r="B18" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>135985442</v>
       </c>
       <c r="B19" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135985427</v>
       </c>
       <c r="B20" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135985431</v>
       </c>
       <c r="B21" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>135985432</v>
       </c>
       <c r="B22" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135985434</v>
       </c>
       <c r="B23" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>135985435</v>
       </c>
       <c r="B24" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>135985437</v>
       </c>
       <c r="B25" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>135987434</v>
       </c>
       <c r="B26" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>135985433</v>
       </c>
       <c r="B27" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135985438</v>
       </c>
       <c r="B28" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/S 722-2026 artfynd.xlsx
+++ b/artfynd/S 722-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135985429</v>
       </c>
       <c r="B2" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135985436</v>
       </c>
       <c r="B3" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136146808</v>
       </c>
       <c r="B4" t="n">
-        <v>57878</v>
+        <v>57891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136146809</v>
       </c>
       <c r="B5" t="n">
-        <v>57878</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>136146804</v>
       </c>
       <c r="B6" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136146806</v>
       </c>
       <c r="B7" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>135985424</v>
       </c>
       <c r="B17" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>135985441</v>
       </c>
       <c r="B18" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>135985442</v>
       </c>
       <c r="B19" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135985427</v>
       </c>
       <c r="B20" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135985431</v>
       </c>
       <c r="B21" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>135985432</v>
       </c>
       <c r="B22" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135985434</v>
       </c>
       <c r="B23" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>135985435</v>
       </c>
       <c r="B24" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>135985437</v>
       </c>
       <c r="B25" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>135987434</v>
       </c>
       <c r="B26" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>135985433</v>
       </c>
       <c r="B27" t="n">
-        <v>98379</v>
+        <v>98392</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135985438</v>
       </c>
       <c r="B28" t="n">
-        <v>98379</v>
+        <v>98392</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>135985428</v>
       </c>
       <c r="B29" t="n">
-        <v>87256</v>
+        <v>87269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/S 722-2026 artfynd.xlsx
+++ b/artfynd/S 722-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135985429</v>
       </c>
       <c r="B2" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135985436</v>
       </c>
       <c r="B3" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>135985424</v>
       </c>
       <c r="B17" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>135985441</v>
       </c>
       <c r="B18" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>135985442</v>
       </c>
       <c r="B19" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135985427</v>
       </c>
       <c r="B20" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135985431</v>
       </c>
       <c r="B21" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>135985432</v>
       </c>
       <c r="B22" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135985434</v>
       </c>
       <c r="B23" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>135985435</v>
       </c>
       <c r="B24" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>135985437</v>
       </c>
       <c r="B25" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>135987434</v>
       </c>
       <c r="B26" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>135985433</v>
       </c>
       <c r="B27" t="n">
-        <v>98392</v>
+        <v>98393</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135985438</v>
       </c>
       <c r="B28" t="n">
-        <v>98392</v>
+        <v>98393</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>135985428</v>
       </c>
       <c r="B29" t="n">
-        <v>87269</v>
+        <v>87270</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
